--- a/Calendario_Digital_Base.xlsx
+++ b/Calendario_Digital_Base.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O249"/>
+  <dimension ref="A1:R249"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -414,9 +414,12 @@
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="15.83203125" customWidth="1"/>
+    <col min="16" max="16" width="15.83203125" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="18" max="18" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,22 +451,31 @@
         <v>HV</v>
       </c>
       <c r="J1" t="str">
-        <v>Inicio</v>
+        <v>Data Inicio</v>
       </c>
       <c r="K1" t="str">
-        <v>Fim</v>
+        <v>Data Fim</v>
       </c>
       <c r="L1" t="str">
         <v>Tecnicos</v>
       </c>
       <c r="M1" t="str">
+        <v>Realizado</v>
+      </c>
+      <c r="N1" t="str">
         <v>Status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Ultima Calibracao</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
+        <v>Proxima Calibracao</v>
+      </c>
+      <c r="Q1" t="str">
         <v>Periodo</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Comentários</v>
       </c>
     </row>
     <row r="2">
@@ -504,13 +516,22 @@
         <v>JC</v>
       </c>
       <c r="M2" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>6</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -551,13 +572,22 @@
         <v>JC</v>
       </c>
       <c r="M3" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -598,13 +628,22 @@
         <v>JC</v>
       </c>
       <c r="M4" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N4" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O4" t="str">
         <v>2024-12-02</v>
       </c>
-      <c r="O4">
+      <c r="P4" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>12</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -645,13 +684,22 @@
         <v>MC</v>
       </c>
       <c r="M5" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>12</v>
+      </c>
+      <c r="R5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -692,13 +740,22 @@
         <v>ES</v>
       </c>
       <c r="M6" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>12</v>
+      </c>
+      <c r="R6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -739,13 +796,22 @@
         <v>ES</v>
       </c>
       <c r="M7" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>12</v>
+      </c>
+      <c r="R7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -786,13 +852,22 @@
         <v>ES</v>
       </c>
       <c r="M8" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>6</v>
+      </c>
+      <c r="R8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -833,13 +908,22 @@
         <v>ES</v>
       </c>
       <c r="M9" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>6</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -880,13 +964,22 @@
         <v>MC</v>
       </c>
       <c r="M10" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N10" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O10" t="str">
         <v>2024-10-14</v>
       </c>
-      <c r="O10">
-        <v>0</v>
+      <c r="P10" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -927,13 +1020,22 @@
         <v>MC</v>
       </c>
       <c r="M11" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <v>12</v>
+      </c>
+      <c r="R11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -974,13 +1076,22 @@
         <v>JC</v>
       </c>
       <c r="M12" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <v>12</v>
+      </c>
+      <c r="R12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1021,13 +1132,22 @@
         <v>JC</v>
       </c>
       <c r="M13" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <v>12</v>
+      </c>
+      <c r="R13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1068,13 +1188,22 @@
         <v>MC</v>
       </c>
       <c r="M14" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <v>12</v>
+      </c>
+      <c r="R14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1115,13 +1244,22 @@
         <v>JC</v>
       </c>
       <c r="M15" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <v>12</v>
+      </c>
+      <c r="R15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1162,13 +1300,22 @@
         <v>LF</v>
       </c>
       <c r="M16" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q16">
         <v>6</v>
+      </c>
+      <c r="R16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1209,13 +1356,22 @@
         <v>MC</v>
       </c>
       <c r="M17" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q17">
         <v>6</v>
+      </c>
+      <c r="R17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1256,13 +1412,22 @@
         <v>JC</v>
       </c>
       <c r="M18" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N18" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O18" t="str">
         <v>2025-03-10</v>
       </c>
-      <c r="O18">
+      <c r="P18" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q18">
         <v>6</v>
+      </c>
+      <c r="R18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1303,13 +1468,22 @@
         <v>CG</v>
       </c>
       <c r="M19" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>24</v>
+      </c>
+      <c r="R19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1350,13 +1524,22 @@
         <v>LF</v>
       </c>
       <c r="M20" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>12</v>
+      </c>
+      <c r="R20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1397,13 +1580,22 @@
         <v>JC</v>
       </c>
       <c r="M21" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <v>12</v>
+      </c>
+      <c r="R21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1444,13 +1636,22 @@
         <v>MC</v>
       </c>
       <c r="M22" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q22">
         <v>12</v>
+      </c>
+      <c r="R22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1491,13 +1692,22 @@
         <v>JC</v>
       </c>
       <c r="M23" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>12</v>
+      </c>
+      <c r="R23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1538,13 +1748,22 @@
         <v>LF</v>
       </c>
       <c r="M24" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N24" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24">
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q24">
         <v>12</v>
+      </c>
+      <c r="R24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1585,13 +1804,22 @@
         <v>ES</v>
       </c>
       <c r="M25" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N25" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25">
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q25">
         <v>12</v>
+      </c>
+      <c r="R25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1632,13 +1860,22 @@
         <v>JC</v>
       </c>
       <c r="M26" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q26">
         <v>12</v>
+      </c>
+      <c r="R26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1679,13 +1916,22 @@
         <v>JC</v>
       </c>
       <c r="M27" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N27" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>2025-01-27</v>
       </c>
-      <c r="O27">
+      <c r="P27" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>6</v>
+      </c>
+      <c r="R27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1726,13 +1972,22 @@
         <v>JC</v>
       </c>
       <c r="M28" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N28" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>2025-02-03</v>
       </c>
-      <c r="O28">
+      <c r="P28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q28">
         <v>6</v>
+      </c>
+      <c r="R28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1773,13 +2028,22 @@
         <v>JC</v>
       </c>
       <c r="M29" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1820,13 +2084,22 @@
         <v>JC</v>
       </c>
       <c r="M30" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N30" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>2024-08-09</v>
       </c>
-      <c r="O30">
+      <c r="P30" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q30">
         <v>6</v>
+      </c>
+      <c r="R30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1867,13 +2140,22 @@
         <v>LF</v>
       </c>
       <c r="M31" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1914,13 +2196,22 @@
         <v>JC</v>
       </c>
       <c r="M32" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N32" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>2024-08-06</v>
       </c>
-      <c r="O32">
+      <c r="P32" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q32">
         <v>6</v>
+      </c>
+      <c r="R32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1961,13 +2252,22 @@
         <v/>
       </c>
       <c r="M33" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N33" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N33" t="str">
-        <v/>
-      </c>
-      <c r="O33">
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q33">
         <v>6</v>
+      </c>
+      <c r="R33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2008,13 +2308,22 @@
         <v>MC</v>
       </c>
       <c r="M34" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N34" t="str">
-        <v/>
-      </c>
-      <c r="O34">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2055,13 +2364,22 @@
         <v>JC</v>
       </c>
       <c r="M35" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N35" t="str">
-        <v/>
-      </c>
-      <c r="O35">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q35">
         <v>12</v>
+      </c>
+      <c r="R35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -2102,13 +2420,22 @@
         <v>LF</v>
       </c>
       <c r="M36" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2149,13 +2476,22 @@
         <v>MC</v>
       </c>
       <c r="M37" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N37" t="str">
-        <v/>
-      </c>
-      <c r="O37">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q37">
         <v>6</v>
+      </c>
+      <c r="R37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2196,13 +2532,22 @@
         <v>JC</v>
       </c>
       <c r="M38" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <v>6</v>
+      </c>
+      <c r="R38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2243,13 +2588,22 @@
         <v>MC</v>
       </c>
       <c r="M39" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N39" t="str">
-        <v/>
-      </c>
-      <c r="O39">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q39">
         <v>12</v>
+      </c>
+      <c r="R39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2290,13 +2644,22 @@
         <v>LF</v>
       </c>
       <c r="M40" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q40">
         <v>12</v>
+      </c>
+      <c r="R40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2337,13 +2700,22 @@
         <v>ES</v>
       </c>
       <c r="M41" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q41">
         <v>12</v>
+      </c>
+      <c r="R41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2384,13 +2756,22 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2431,13 +2812,22 @@
         <v>ES</v>
       </c>
       <c r="M43" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2478,13 +2868,22 @@
         <v>LF</v>
       </c>
       <c r="M44" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q44">
         <v>6</v>
+      </c>
+      <c r="R44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2525,13 +2924,22 @@
         <v>JC</v>
       </c>
       <c r="M45" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2572,13 +2980,22 @@
         <v>MC</v>
       </c>
       <c r="M46" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q46">
         <v>12</v>
+      </c>
+      <c r="R46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2619,13 +3036,22 @@
         <v>MC</v>
       </c>
       <c r="M47" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N47" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O47" t="str">
         <v>2024-07-22</v>
       </c>
-      <c r="O47">
+      <c r="P47" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q47">
         <v>6</v>
+      </c>
+      <c r="R47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2666,13 +3092,22 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="O48">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2713,13 +3148,22 @@
         <v>JC</v>
       </c>
       <c r="M49" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="O49">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q49">
         <v>12</v>
+      </c>
+      <c r="R49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2760,13 +3204,22 @@
         <v>LF</v>
       </c>
       <c r="M50" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q50">
         <v>12</v>
+      </c>
+      <c r="R50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2807,13 +3260,22 @@
         <v>ES</v>
       </c>
       <c r="M51" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N51" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O51" t="str">
         <v>2025-02-03</v>
       </c>
-      <c r="O51">
+      <c r="P51" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q51">
         <v>6</v>
+      </c>
+      <c r="R51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2854,13 +3316,22 @@
         <v>LF</v>
       </c>
       <c r="M52" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N52" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O52" t="str">
         <v>2024-06-11</v>
       </c>
-      <c r="O52">
+      <c r="P52" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q52">
         <v>12</v>
+      </c>
+      <c r="R52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -2901,13 +3372,22 @@
         <v>LF</v>
       </c>
       <c r="M53" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="O53">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q53">
         <v>6</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2948,13 +3428,22 @@
         <v>LF</v>
       </c>
       <c r="M54" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N54" t="str">
-        <v/>
-      </c>
-      <c r="O54">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q54">
         <v>12</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2995,13 +3484,22 @@
         <v>MC</v>
       </c>
       <c r="M55" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="O55">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -3042,13 +3540,22 @@
         <v>ES</v>
       </c>
       <c r="M56" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="O56">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q56">
         <v>12</v>
+      </c>
+      <c r="R56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -3089,13 +3596,22 @@
         <v>ES</v>
       </c>
       <c r="M57" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q57">
         <v>6</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -3136,13 +3652,22 @@
         <v>JC</v>
       </c>
       <c r="M58" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -3183,13 +3708,22 @@
         <v>ES</v>
       </c>
       <c r="M59" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N59" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O59" t="str">
         <v>2025-01-27</v>
       </c>
-      <c r="O59">
+      <c r="P59" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q59">
         <v>6</v>
+      </c>
+      <c r="R59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3230,13 +3764,22 @@
         <v>LF</v>
       </c>
       <c r="M60" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -3277,13 +3820,22 @@
         <v>MC</v>
       </c>
       <c r="M61" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q61">
         <v>12</v>
+      </c>
+      <c r="R61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -3324,13 +3876,22 @@
         <v>ES</v>
       </c>
       <c r="M62" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N62" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>2026-01-23</v>
       </c>
-      <c r="O62">
+      <c r="P62" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q62">
         <v>12</v>
+      </c>
+      <c r="R62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -3371,13 +3932,22 @@
         <v>ES</v>
       </c>
       <c r="M63" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O63" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63">
         <v>12</v>
+      </c>
+      <c r="R63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -3418,13 +3988,22 @@
         <v>LF, CG</v>
       </c>
       <c r="M64" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N64" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O64" t="str">
         <v>2026-01-09</v>
       </c>
-      <c r="O64">
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64">
         <v>6</v>
+      </c>
+      <c r="R64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -3465,13 +4044,22 @@
         <v>LF</v>
       </c>
       <c r="M65" t="str">
-        <v>Férias / Bloqueio</v>
+        <v>Sim</v>
       </c>
       <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O65" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65">
         <v>12</v>
+      </c>
+      <c r="R65" t="str">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -3512,13 +4100,22 @@
         <v>JC, CG</v>
       </c>
       <c r="M66" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O66" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66">
         <v>36</v>
+      </c>
+      <c r="R66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -3559,13 +4156,22 @@
         <v>JC</v>
       </c>
       <c r="M67" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O67" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67">
         <v>6</v>
+      </c>
+      <c r="R67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -3606,13 +4212,22 @@
         <v>JC</v>
       </c>
       <c r="M68" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O68" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68">
         <v>6</v>
+      </c>
+      <c r="R68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -3653,13 +4268,22 @@
         <v>MC</v>
       </c>
       <c r="M69" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N69" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O69" t="str">
         <v>2026-01-09</v>
       </c>
-      <c r="O69">
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69">
         <v>6</v>
+      </c>
+      <c r="R69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -3700,13 +4324,22 @@
         <v>MC, CG</v>
       </c>
       <c r="M70" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N70" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O70" t="str">
         <v>2026-01-20</v>
       </c>
-      <c r="O70">
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70">
         <v>6</v>
+      </c>
+      <c r="R70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3747,13 +4380,22 @@
         <v>AP, LF, MC</v>
       </c>
       <c r="M71" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N71" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O71" t="str">
         <v>2026-02-02</v>
       </c>
-      <c r="O71">
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71">
         <v>6</v>
+      </c>
+      <c r="R71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3794,13 +4436,22 @@
         <v/>
       </c>
       <c r="M72" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O72" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72">
         <v>6</v>
+      </c>
+      <c r="R72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -3841,13 +4492,22 @@
         <v/>
       </c>
       <c r="M73" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O73" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73">
         <v>6</v>
+      </c>
+      <c r="R73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3888,13 +4548,22 @@
         <v>ES</v>
       </c>
       <c r="M74" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O74" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74">
         <v>12</v>
+      </c>
+      <c r="R74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -3935,13 +4604,22 @@
         <v>ES</v>
       </c>
       <c r="M75" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O75" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -3982,13 +4660,22 @@
         <v>LF</v>
       </c>
       <c r="M76" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="O76">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O76" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76" t="str">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -4029,13 +4716,22 @@
         <v>LF</v>
       </c>
       <c r="M77" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O77" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -4076,13 +4772,22 @@
         <v>LF</v>
       </c>
       <c r="M78" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O78" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78" t="str">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -4123,13 +4828,22 @@
         <v>JC</v>
       </c>
       <c r="M79" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O79" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -4170,13 +4884,22 @@
         <v>JC</v>
       </c>
       <c r="M80" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O80" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -4217,13 +4940,22 @@
         <v>JC</v>
       </c>
       <c r="M81" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O81" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81" t="str">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -4264,13 +4996,22 @@
         <v>JC</v>
       </c>
       <c r="M82" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O82" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82" t="str">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -4311,13 +5052,22 @@
         <v>JC</v>
       </c>
       <c r="M83" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O83" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83" t="str">
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -4358,13 +5108,22 @@
         <v>MC</v>
       </c>
       <c r="M84" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="O84">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O84" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84" t="str">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -4405,13 +5164,22 @@
         <v>MC</v>
       </c>
       <c r="M85" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O85" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -4452,13 +5220,22 @@
         <v>MC</v>
       </c>
       <c r="M86" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O86" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -4499,13 +5276,22 @@
         <v>MC</v>
       </c>
       <c r="M87" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="O87">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O87" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87" t="str">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -4546,13 +5332,22 @@
         <v>MC</v>
       </c>
       <c r="M88" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N88" t="str">
-        <v/>
-      </c>
-      <c r="O88">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O88" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88">
         <v>12</v>
+      </c>
+      <c r="R88" t="str">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -4593,13 +5388,22 @@
         <v>MC</v>
       </c>
       <c r="M89" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="O89">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O89" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -4640,13 +5444,22 @@
         <v>AP</v>
       </c>
       <c r="M90" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="O90">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O90" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90" t="str">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -4687,13 +5500,22 @@
         <v/>
       </c>
       <c r="M91" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O91" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91" t="str">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -4734,13 +5556,22 @@
         <v/>
       </c>
       <c r="M92" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N92" t="str">
-        <v/>
-      </c>
-      <c r="O92">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O92" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -4781,13 +5612,22 @@
         <v>ES</v>
       </c>
       <c r="M93" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N93" t="str">
-        <v/>
-      </c>
-      <c r="O93">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O93" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -4828,13 +5668,22 @@
         <v>ES</v>
       </c>
       <c r="M94" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O94" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94" t="str">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -4875,13 +5724,22 @@
         <v>LF</v>
       </c>
       <c r="M95" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="O95">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O95" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95" t="str">
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -4922,13 +5780,22 @@
         <v>LF</v>
       </c>
       <c r="M96" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N96" t="str">
-        <v/>
-      </c>
-      <c r="O96">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O96" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -4969,13 +5836,22 @@
         <v>LF</v>
       </c>
       <c r="M97" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N97" t="str">
-        <v/>
-      </c>
-      <c r="O97">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O97" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -5016,13 +5892,22 @@
         <v>LF</v>
       </c>
       <c r="M98" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N98" t="str">
-        <v/>
-      </c>
-      <c r="O98">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O98" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98" t="str">
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -5063,13 +5948,22 @@
         <v>JC</v>
       </c>
       <c r="M99" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="O99">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O99" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99" t="str">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -5110,13 +6004,22 @@
         <v>JC</v>
       </c>
       <c r="M100" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="O100">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O100" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100" t="str">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -5157,13 +6060,22 @@
         <v>JC</v>
       </c>
       <c r="M101" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N101" t="str">
-        <v/>
-      </c>
-      <c r="O101">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O101" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -5204,13 +6116,22 @@
         <v>JC</v>
       </c>
       <c r="M102" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="O102">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O102" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -5251,13 +6172,22 @@
         <v>MC</v>
       </c>
       <c r="M103" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N103" t="str">
-        <v/>
-      </c>
-      <c r="O103">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O103" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -5298,13 +6228,22 @@
         <v>MC</v>
       </c>
       <c r="M104" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N104" t="str">
-        <v/>
-      </c>
-      <c r="O104">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O104" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="R104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -5345,13 +6284,22 @@
         <v>MC</v>
       </c>
       <c r="M105" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N105" t="str">
-        <v/>
-      </c>
-      <c r="O105">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O105" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -5392,13 +6340,22 @@
         <v/>
       </c>
       <c r="M106" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N106" t="str">
-        <v/>
-      </c>
-      <c r="O106">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O106" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+      <c r="R106" t="str">
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -5439,13 +6396,22 @@
         <v>ES</v>
       </c>
       <c r="M107" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N107" t="str">
-        <v/>
-      </c>
-      <c r="O107">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O107" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+      <c r="R107" t="str">
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -5486,13 +6452,22 @@
         <v>LF</v>
       </c>
       <c r="M108" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N108" t="str">
-        <v/>
-      </c>
-      <c r="O108">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O108" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108" t="str">
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -5533,13 +6508,22 @@
         <v>LF</v>
       </c>
       <c r="M109" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N109" t="str">
-        <v/>
-      </c>
-      <c r="O109">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O109" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109" t="str">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -5580,13 +6564,22 @@
         <v>JC</v>
       </c>
       <c r="M110" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N110" t="str">
-        <v/>
-      </c>
-      <c r="O110">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O110" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110" t="str">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -5627,13 +6620,22 @@
         <v>JC</v>
       </c>
       <c r="M111" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N111" t="str">
-        <v/>
-      </c>
-      <c r="O111">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O111" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111" t="str">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -5674,13 +6676,22 @@
         <v>JC</v>
       </c>
       <c r="M112" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N112" t="str">
-        <v/>
-      </c>
-      <c r="O112">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O112" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112" t="str">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -5721,13 +6732,22 @@
         <v>MC</v>
       </c>
       <c r="M113" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N113" t="str">
-        <v/>
-      </c>
-      <c r="O113">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O113" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -5768,13 +6788,22 @@
         <v>MC</v>
       </c>
       <c r="M114" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N114" t="str">
-        <v/>
-      </c>
-      <c r="O114">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O114" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114" t="str">
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -5815,13 +6844,22 @@
         <v>MC</v>
       </c>
       <c r="M115" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N115" t="str">
-        <v/>
-      </c>
-      <c r="O115">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O115" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115" t="str">
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -5862,13 +6900,22 @@
         <v/>
       </c>
       <c r="M116" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N116" t="str">
-        <v/>
-      </c>
-      <c r="O116">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O116" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116">
+        <v>0</v>
+      </c>
+      <c r="R116" t="str">
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -5909,13 +6956,22 @@
         <v/>
       </c>
       <c r="M117" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N117" t="str">
-        <v/>
-      </c>
-      <c r="O117">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O117" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117">
+        <v>0</v>
+      </c>
+      <c r="R117" t="str">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -5956,13 +7012,22 @@
         <v/>
       </c>
       <c r="M118" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N118" t="str">
-        <v/>
-      </c>
-      <c r="O118">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O118" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118" t="str">
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -6003,13 +7068,22 @@
         <v>ES</v>
       </c>
       <c r="M119" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N119" t="str">
-        <v/>
-      </c>
-      <c r="O119">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O119" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119" t="str">
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -6050,13 +7124,22 @@
         <v>ES</v>
       </c>
       <c r="M120" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N120" t="str">
-        <v/>
-      </c>
-      <c r="O120">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O120" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120" t="str">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -6097,13 +7180,22 @@
         <v>ES</v>
       </c>
       <c r="M121" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N121" t="str">
-        <v/>
-      </c>
-      <c r="O121">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O121" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121" t="str">
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -6144,13 +7236,22 @@
         <v>LF</v>
       </c>
       <c r="M122" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N122" t="str">
-        <v/>
-      </c>
-      <c r="O122">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O122" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122" t="str">
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -6191,13 +7292,22 @@
         <v>LF</v>
       </c>
       <c r="M123" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N123" t="str">
-        <v/>
-      </c>
-      <c r="O123">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O123" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123" t="str">
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -6238,13 +7348,22 @@
         <v>JC</v>
       </c>
       <c r="M124" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N124" t="str">
-        <v/>
-      </c>
-      <c r="O124">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O124" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124" t="str">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -6285,13 +7404,22 @@
         <v>JC</v>
       </c>
       <c r="M125" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N125" t="str">
-        <v/>
-      </c>
-      <c r="O125">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O125" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125" t="str">
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -6332,13 +7460,22 @@
         <v>JC</v>
       </c>
       <c r="M126" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N126" t="str">
-        <v/>
-      </c>
-      <c r="O126">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O126" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126" t="str">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -6379,13 +7516,22 @@
         <v>MC</v>
       </c>
       <c r="M127" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N127" t="str">
-        <v/>
-      </c>
-      <c r="O127">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O127" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127" t="str">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -6426,13 +7572,22 @@
         <v>MC</v>
       </c>
       <c r="M128" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N128" t="str">
-        <v/>
-      </c>
-      <c r="O128">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O128" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -6473,13 +7628,22 @@
         <v>MC</v>
       </c>
       <c r="M129" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N129" t="str">
-        <v/>
-      </c>
-      <c r="O129">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O129" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129" t="str">
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -6520,13 +7684,22 @@
         <v>AP</v>
       </c>
       <c r="M130" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N130" t="str">
-        <v/>
-      </c>
-      <c r="O130">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O130" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130" t="str">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -6567,13 +7740,22 @@
         <v>AP</v>
       </c>
       <c r="M131" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N131" t="str">
-        <v/>
-      </c>
-      <c r="O131">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O131" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131" t="str">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -6614,13 +7796,22 @@
         <v>AP</v>
       </c>
       <c r="M132" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N132" t="str">
-        <v/>
-      </c>
-      <c r="O132">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O132" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132" t="str">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -6661,13 +7852,22 @@
         <v/>
       </c>
       <c r="M133" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N133" t="str">
-        <v/>
-      </c>
-      <c r="O133">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O133" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133" t="str">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -6708,13 +7908,22 @@
         <v/>
       </c>
       <c r="M134" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N134" t="str">
-        <v/>
-      </c>
-      <c r="O134">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O134" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134" t="str">
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -6755,13 +7964,22 @@
         <v>ES</v>
       </c>
       <c r="M135" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N135" t="str">
-        <v/>
-      </c>
-      <c r="O135">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O135" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135" t="str">
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -6802,13 +8020,22 @@
         <v>ES</v>
       </c>
       <c r="M136" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N136" t="str">
-        <v/>
-      </c>
-      <c r="O136">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O136" t="str">
+        <v>2026-06-24</v>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136" t="str">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -6849,13 +8076,22 @@
         <v>ES</v>
       </c>
       <c r="M137" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N137" t="str">
-        <v/>
-      </c>
-      <c r="O137">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O137" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137" t="str">
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -6896,13 +8132,22 @@
         <v>LF</v>
       </c>
       <c r="M138" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N138" t="str">
-        <v/>
-      </c>
-      <c r="O138">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O138" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138" t="str">
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -6943,13 +8188,22 @@
         <v>LF</v>
       </c>
       <c r="M139" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N139" t="str">
-        <v/>
-      </c>
-      <c r="O139">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O139" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139" t="str">
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -6990,13 +8244,22 @@
         <v>JC</v>
       </c>
       <c r="M140" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N140" t="str">
-        <v/>
-      </c>
-      <c r="O140">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O140" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140">
         <v>6</v>
+      </c>
+      <c r="R140" t="str">
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -7037,13 +8300,22 @@
         <v>JC</v>
       </c>
       <c r="M141" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N141" t="str">
-        <v/>
-      </c>
-      <c r="O141">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O141" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141">
         <v>6</v>
+      </c>
+      <c r="R141" t="str">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -7084,13 +8356,22 @@
         <v>JC</v>
       </c>
       <c r="M142" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N142" t="str">
-        <v/>
-      </c>
-      <c r="O142">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O142" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142">
+        <v>0</v>
+      </c>
+      <c r="R142" t="str">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -7131,13 +8412,22 @@
         <v>MC</v>
       </c>
       <c r="M143" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N143" t="str">
-        <v/>
-      </c>
-      <c r="O143">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O143" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143">
+        <v>0</v>
+      </c>
+      <c r="R143" t="str">
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -7178,13 +8468,22 @@
         <v>MC</v>
       </c>
       <c r="M144" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N144" t="str">
-        <v/>
-      </c>
-      <c r="O144">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O144" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144">
+        <v>0</v>
+      </c>
+      <c r="R144" t="str">
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -7225,13 +8524,22 @@
         <v>MC</v>
       </c>
       <c r="M145" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N145" t="str">
-        <v/>
-      </c>
-      <c r="O145">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O145" t="str">
+        <v>2026-06-24</v>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145">
+        <v>0</v>
+      </c>
+      <c r="R145" t="str">
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -7272,13 +8580,22 @@
         <v>MC</v>
       </c>
       <c r="M146" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N146" t="str">
-        <v/>
-      </c>
-      <c r="O146">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O146" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146">
+        <v>0</v>
+      </c>
+      <c r="R146" t="str">
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -7319,13 +8636,22 @@
         <v>AP</v>
       </c>
       <c r="M147" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N147" t="str">
-        <v/>
-      </c>
-      <c r="O147">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O147" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147">
+        <v>0</v>
+      </c>
+      <c r="R147" t="str">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -7366,13 +8692,22 @@
         <v>ES</v>
       </c>
       <c r="M148" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N148" t="str">
-        <v/>
-      </c>
-      <c r="O148">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O148" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148">
+        <v>0</v>
+      </c>
+      <c r="R148" t="str">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -7413,13 +8748,22 @@
         <v>ES</v>
       </c>
       <c r="M149" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N149" t="str">
-        <v/>
-      </c>
-      <c r="O149">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O149" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149">
+        <v>0</v>
+      </c>
+      <c r="R149" t="str">
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -7460,13 +8804,22 @@
         <v>ES</v>
       </c>
       <c r="M150" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N150" t="str">
-        <v/>
-      </c>
-      <c r="O150">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O150" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150">
+        <v>0</v>
+      </c>
+      <c r="R150" t="str">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -7507,13 +8860,22 @@
         <v>ES, LF</v>
       </c>
       <c r="M151" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N151" t="str">
-        <v>2026-01-05</v>
-      </c>
-      <c r="O151">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O151" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151">
         <v>6</v>
+      </c>
+      <c r="R151" t="str">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -7554,13 +8916,22 @@
         <v>LF</v>
       </c>
       <c r="M152" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N152" t="str">
-        <v/>
-      </c>
-      <c r="O152">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O152" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152">
+        <v>0</v>
+      </c>
+      <c r="R152" t="str">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -7601,13 +8972,22 @@
         <v>LF</v>
       </c>
       <c r="M153" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N153" t="str">
-        <v/>
-      </c>
-      <c r="O153">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O153" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153">
+        <v>0</v>
+      </c>
+      <c r="R153" t="str">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -7648,13 +9028,22 @@
         <v>JC</v>
       </c>
       <c r="M154" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N154" t="str">
-        <v/>
-      </c>
-      <c r="O154">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O154" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154" t="str">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -7695,13 +9084,22 @@
         <v>JC</v>
       </c>
       <c r="M155" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O155" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155" t="str">
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -7742,13 +9140,22 @@
         <v>JC</v>
       </c>
       <c r="M156" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N156" t="str">
-        <v/>
-      </c>
-      <c r="O156">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O156" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156" t="str">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -7789,13 +9196,22 @@
         <v>JC</v>
       </c>
       <c r="M157" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O157" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157">
         <v>12</v>
+      </c>
+      <c r="R157" t="str">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -7836,13 +9252,22 @@
         <v>MC</v>
       </c>
       <c r="M158" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N158" t="str">
-        <v/>
-      </c>
-      <c r="O158">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O158" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158">
+        <v>0</v>
+      </c>
+      <c r="R158" t="str">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -7883,13 +9308,22 @@
         <v>MC</v>
       </c>
       <c r="M159" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N159" t="str">
-        <v/>
-      </c>
-      <c r="O159">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O159" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159">
+        <v>0</v>
+      </c>
+      <c r="R159" t="str">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -7930,13 +9364,22 @@
         <v>MC</v>
       </c>
       <c r="M160" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N160" t="str">
-        <v/>
-      </c>
-      <c r="O160">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O160" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160">
+        <v>0</v>
+      </c>
+      <c r="R160" t="str">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -7977,13 +9420,22 @@
         <v>AP</v>
       </c>
       <c r="M161" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N161" t="str">
-        <v/>
-      </c>
-      <c r="O161">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O161" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161">
+        <v>0</v>
+      </c>
+      <c r="R161" t="str">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -8024,13 +9476,22 @@
         <v>AP</v>
       </c>
       <c r="M162" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N162" t="str">
-        <v/>
-      </c>
-      <c r="O162">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O162" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162">
+        <v>0</v>
+      </c>
+      <c r="R162" t="str">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -8071,13 +9532,22 @@
         <v>ES</v>
       </c>
       <c r="M163" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O163" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163">
+        <v>0</v>
+      </c>
+      <c r="R163" t="str">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -8118,13 +9588,22 @@
         <v>ES</v>
       </c>
       <c r="M164" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N164" t="str">
-        <v/>
-      </c>
-      <c r="O164">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O164" t="str">
+        <v>2026-08-21</v>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164">
+        <v>0</v>
+      </c>
+      <c r="R164" t="str">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -8165,13 +9644,22 @@
         <v>ES</v>
       </c>
       <c r="M165" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N165" t="str">
-        <v/>
-      </c>
-      <c r="O165">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O165" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165">
+        <v>0</v>
+      </c>
+      <c r="R165" t="str">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -8212,13 +9700,22 @@
         <v>LF</v>
       </c>
       <c r="M166" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N166" t="str">
-        <v/>
-      </c>
-      <c r="O166">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O166" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166">
+        <v>0</v>
+      </c>
+      <c r="R166" t="str">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -8259,13 +9756,22 @@
         <v>JC</v>
       </c>
       <c r="M167" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N167" t="str">
-        <v/>
-      </c>
-      <c r="O167">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O167" t="str">
+        <v>2026-08-07</v>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167">
+        <v>0</v>
+      </c>
+      <c r="R167" t="str">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -8306,13 +9812,22 @@
         <v>JC</v>
       </c>
       <c r="M168" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N168" t="str">
-        <v/>
-      </c>
-      <c r="O168">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O168" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168">
+        <v>0</v>
+      </c>
+      <c r="R168" t="str">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -8353,13 +9868,22 @@
         <v>JC</v>
       </c>
       <c r="M169" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N169" t="str">
-        <v/>
-      </c>
-      <c r="O169">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O169" t="str">
+        <v>2026-08-21</v>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169">
+        <v>0</v>
+      </c>
+      <c r="R169" t="str">
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -8400,13 +9924,22 @@
         <v>JC</v>
       </c>
       <c r="M170" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N170" t="str">
-        <v/>
-      </c>
-      <c r="O170">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O170" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170">
+        <v>0</v>
+      </c>
+      <c r="R170" t="str">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -8447,13 +9980,22 @@
         <v>MC</v>
       </c>
       <c r="M171" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N171" t="str">
-        <v/>
-      </c>
-      <c r="O171">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O171" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171" t="str">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -8494,13 +10036,22 @@
         <v>MC</v>
       </c>
       <c r="M172" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N172" t="str">
-        <v/>
-      </c>
-      <c r="O172">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O172" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172">
         <v>12</v>
+      </c>
+      <c r="R172" t="str">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -8541,13 +10092,22 @@
         <v>MC</v>
       </c>
       <c r="M173" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N173" t="str">
-        <v/>
-      </c>
-      <c r="O173">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O173" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173">
         <v>12</v>
+      </c>
+      <c r="R173" t="str">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -8588,13 +10148,22 @@
         <v>MC</v>
       </c>
       <c r="M174" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N174" t="str">
-        <v/>
-      </c>
-      <c r="O174">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O174" t="str">
+        <v>2026-08-26</v>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174">
+        <v>0</v>
+      </c>
+      <c r="R174" t="str">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -8635,13 +10204,22 @@
         <v>MC</v>
       </c>
       <c r="M175" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N175" t="str">
-        <v/>
-      </c>
-      <c r="O175">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O175" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175">
+        <v>0</v>
+      </c>
+      <c r="R175" t="str">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -8682,13 +10260,22 @@
         <v>AP</v>
       </c>
       <c r="M176" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N176" t="str">
-        <v/>
-      </c>
-      <c r="O176">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O176" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176">
+        <v>0</v>
+      </c>
+      <c r="R176" t="str">
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -8729,13 +10316,22 @@
         <v>AP</v>
       </c>
       <c r="M177" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N177" t="str">
-        <v/>
-      </c>
-      <c r="O177">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O177" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177">
+        <v>0</v>
+      </c>
+      <c r="R177" t="str">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -8776,13 +10372,22 @@
         <v>AP</v>
       </c>
       <c r="M178" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N178" t="str">
-        <v/>
-      </c>
-      <c r="O178">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O178" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178">
+        <v>0</v>
+      </c>
+      <c r="R178" t="str">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -8823,13 +10428,22 @@
         <v/>
       </c>
       <c r="M179" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N179" t="str">
-        <v/>
-      </c>
-      <c r="O179">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O179" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179">
+        <v>0</v>
+      </c>
+      <c r="R179" t="str">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -8870,13 +10484,22 @@
         <v>ES</v>
       </c>
       <c r="M180" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N180" t="str">
-        <v/>
-      </c>
-      <c r="O180">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O180" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180">
+        <v>0</v>
+      </c>
+      <c r="R180" t="str">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -8917,13 +10540,22 @@
         <v>ES</v>
       </c>
       <c r="M181" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N181" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N181" t="str">
-        <v/>
-      </c>
-      <c r="O181">
-        <v>0</v>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q181">
+        <v>0</v>
+      </c>
+      <c r="R181" t="str">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -8964,13 +10596,22 @@
         <v>ES</v>
       </c>
       <c r="M182" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N182" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N182" t="str">
-        <v/>
-      </c>
-      <c r="O182">
-        <v>0</v>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q182">
+        <v>0</v>
+      </c>
+      <c r="R182" t="str">
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -9011,13 +10652,22 @@
         <v>LF</v>
       </c>
       <c r="M183" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N183" t="str">
-        <v/>
-      </c>
-      <c r="O183">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O183" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183">
+        <v>0</v>
+      </c>
+      <c r="R183" t="str">
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -9058,13 +10708,22 @@
         <v>LF</v>
       </c>
       <c r="M184" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N184" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N184" t="str">
-        <v/>
-      </c>
-      <c r="O184">
-        <v>0</v>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q184">
+        <v>0</v>
+      </c>
+      <c r="R184" t="str">
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -9105,13 +10764,22 @@
         <v>JC</v>
       </c>
       <c r="M185" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N185" t="str">
-        <v/>
-      </c>
-      <c r="O185">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O185" t="str">
+        <v>2026-09-04</v>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185" t="str">
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -9152,13 +10820,22 @@
         <v>JC</v>
       </c>
       <c r="M186" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N186" t="str">
-        <v/>
-      </c>
-      <c r="O186">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O186" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186">
+        <v>0</v>
+      </c>
+      <c r="R186" t="str">
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -9199,13 +10876,22 @@
         <v>JC</v>
       </c>
       <c r="M187" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N187" t="str">
-        <v/>
-      </c>
-      <c r="O187">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O187" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187">
+        <v>0</v>
+      </c>
+      <c r="R187" t="str">
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -9246,13 +10932,22 @@
         <v>JC</v>
       </c>
       <c r="M188" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N188" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N188" t="str">
-        <v/>
-      </c>
-      <c r="O188">
-        <v>0</v>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q188">
+        <v>0</v>
+      </c>
+      <c r="R188" t="str">
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -9293,13 +10988,22 @@
         <v>JC</v>
       </c>
       <c r="M189" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N189" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N189" t="str">
-        <v/>
-      </c>
-      <c r="O189">
-        <v>0</v>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q189">
+        <v>0</v>
+      </c>
+      <c r="R189" t="str">
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -9340,13 +11044,22 @@
         <v>JC</v>
       </c>
       <c r="M190" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N190" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N190" t="str">
-        <v/>
-      </c>
-      <c r="O190">
-        <v>0</v>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190" t="str">
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -9387,13 +11100,22 @@
         <v>MC</v>
       </c>
       <c r="M191" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N191" t="str">
-        <v/>
-      </c>
-      <c r="O191">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O191" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191">
+        <v>0</v>
+      </c>
+      <c r="R191" t="str">
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -9434,13 +11156,22 @@
         <v>AP</v>
       </c>
       <c r="M192" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N192" t="str">
-        <v/>
-      </c>
-      <c r="O192">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O192" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192">
+        <v>0</v>
+      </c>
+      <c r="R192" t="str">
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -9481,13 +11212,22 @@
         <v>AP</v>
       </c>
       <c r="M193" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N193" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N193" t="str">
-        <v/>
-      </c>
-      <c r="O193">
-        <v>0</v>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q193">
+        <v>0</v>
+      </c>
+      <c r="R193" t="str">
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -9528,13 +11268,22 @@
         <v/>
       </c>
       <c r="M194" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N194" t="str">
-        <v/>
-      </c>
-      <c r="O194">
-        <v>0</v>
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O194" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194">
+        <v>0</v>
+      </c>
+      <c r="R194" t="str">
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -9575,13 +11324,22 @@
         <v/>
       </c>
       <c r="M195" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N195" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N195" t="str">
-        <v/>
-      </c>
-      <c r="O195">
-        <v>0</v>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q195">
+        <v>0</v>
+      </c>
+      <c r="R195" t="str">
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -9622,13 +11380,22 @@
         <v>ES</v>
       </c>
       <c r="M196" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N196" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N196" t="str">
-        <v/>
-      </c>
-      <c r="O196">
-        <v>0</v>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q196">
+        <v>0</v>
+      </c>
+      <c r="R196" t="str">
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -9669,13 +11436,22 @@
         <v>ES</v>
       </c>
       <c r="M197" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N197" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N197" t="str">
-        <v/>
-      </c>
-      <c r="O197">
-        <v>0</v>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q197">
+        <v>0</v>
+      </c>
+      <c r="R197" t="str">
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -9716,13 +11492,22 @@
         <v>LF</v>
       </c>
       <c r="M198" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N198" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N198" t="str">
-        <v/>
-      </c>
-      <c r="O198">
-        <v>0</v>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q198">
+        <v>0</v>
+      </c>
+      <c r="R198" t="str">
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -9763,13 +11548,22 @@
         <v>LF</v>
       </c>
       <c r="M199" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N199" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N199" t="str">
-        <v/>
-      </c>
-      <c r="O199">
-        <v>0</v>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q199">
+        <v>0</v>
+      </c>
+      <c r="R199" t="str">
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -9810,13 +11604,22 @@
         <v>LF</v>
       </c>
       <c r="M200" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N200" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N200" t="str">
-        <v/>
-      </c>
-      <c r="O200">
-        <v>0</v>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q200">
+        <v>0</v>
+      </c>
+      <c r="R200" t="str">
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -9857,13 +11660,22 @@
         <v>JC</v>
       </c>
       <c r="M201" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N201" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N201" t="str">
-        <v/>
-      </c>
-      <c r="O201">
-        <v>0</v>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q201">
+        <v>0</v>
+      </c>
+      <c r="R201" t="str">
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -9904,13 +11716,22 @@
         <v>JC</v>
       </c>
       <c r="M202" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N202" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N202" t="str">
-        <v/>
-      </c>
-      <c r="O202">
-        <v>0</v>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q202">
+        <v>0</v>
+      </c>
+      <c r="R202" t="str">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -9951,13 +11772,22 @@
         <v>MC</v>
       </c>
       <c r="M203" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N203" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N203" t="str">
-        <v/>
-      </c>
-      <c r="O203">
-        <v>0</v>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q203">
+        <v>0</v>
+      </c>
+      <c r="R203" t="str">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -9998,13 +11828,22 @@
         <v>MC</v>
       </c>
       <c r="M204" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N204" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N204" t="str">
-        <v/>
-      </c>
-      <c r="O204">
-        <v>0</v>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>0</v>
+      </c>
+      <c r="R204" t="str">
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -10045,13 +11884,22 @@
         <v>MC</v>
       </c>
       <c r="M205" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N205" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N205" t="str">
-        <v/>
-      </c>
-      <c r="O205">
-        <v>0</v>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>0</v>
+      </c>
+      <c r="R205" t="str">
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -10092,13 +11940,22 @@
         <v>AP</v>
       </c>
       <c r="M206" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N206" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N206" t="str">
-        <v/>
-      </c>
-      <c r="O206">
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q206">
         <v>12</v>
+      </c>
+      <c r="R206" t="str">
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -10139,13 +11996,22 @@
         <v>AP</v>
       </c>
       <c r="M207" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N207" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N207" t="str">
-        <v/>
-      </c>
-      <c r="O207">
-        <v>0</v>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q207">
+        <v>0</v>
+      </c>
+      <c r="R207" t="str">
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -10186,13 +12052,22 @@
         <v>AP</v>
       </c>
       <c r="M208" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N208" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N208" t="str">
-        <v/>
-      </c>
-      <c r="O208">
-        <v>0</v>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q208">
+        <v>0</v>
+      </c>
+      <c r="R208" t="str">
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -10233,13 +12108,22 @@
         <v>AP</v>
       </c>
       <c r="M209" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N209" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N209" t="str">
-        <v/>
-      </c>
-      <c r="O209">
-        <v>0</v>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q209">
+        <v>0</v>
+      </c>
+      <c r="R209" t="str">
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -10280,13 +12164,22 @@
         <v>ES</v>
       </c>
       <c r="M210" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N210" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N210" t="str">
-        <v/>
-      </c>
-      <c r="O210">
-        <v>0</v>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>0</v>
+      </c>
+      <c r="R210" t="str">
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -10327,13 +12220,22 @@
         <v>ES</v>
       </c>
       <c r="M211" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N211" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N211" t="str">
-        <v/>
-      </c>
-      <c r="O211">
-        <v>0</v>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q211">
+        <v>0</v>
+      </c>
+      <c r="R211" t="str">
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -10374,13 +12276,22 @@
         <v>ES</v>
       </c>
       <c r="M212" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N212" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N212" t="str">
-        <v/>
-      </c>
-      <c r="O212">
-        <v>0</v>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q212">
+        <v>0</v>
+      </c>
+      <c r="R212" t="str">
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -10421,13 +12332,22 @@
         <v>ES</v>
       </c>
       <c r="M213" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N213" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N213" t="str">
-        <v/>
-      </c>
-      <c r="O213">
-        <v>0</v>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q213">
+        <v>0</v>
+      </c>
+      <c r="R213" t="str">
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -10468,13 +12388,22 @@
         <v>LF</v>
       </c>
       <c r="M214" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N214" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N214" t="str">
-        <v/>
-      </c>
-      <c r="O214">
-        <v>0</v>
+      <c r="O214" t="str">
+        <v/>
+      </c>
+      <c r="P214" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q214">
+        <v>0</v>
+      </c>
+      <c r="R214" t="str">
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -10515,13 +12444,22 @@
         <v>LF</v>
       </c>
       <c r="M215" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N215" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N215" t="str">
-        <v/>
-      </c>
-      <c r="O215">
-        <v>0</v>
+      <c r="O215" t="str">
+        <v/>
+      </c>
+      <c r="P215" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>0</v>
+      </c>
+      <c r="R215" t="str">
+        <v/>
       </c>
     </row>
     <row r="216">
@@ -10562,13 +12500,22 @@
         <v>LF</v>
       </c>
       <c r="M216" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N216" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N216" t="str">
-        <v/>
-      </c>
-      <c r="O216">
-        <v>0</v>
+      <c r="O216" t="str">
+        <v/>
+      </c>
+      <c r="P216" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>0</v>
+      </c>
+      <c r="R216" t="str">
+        <v/>
       </c>
     </row>
     <row r="217">
@@ -10609,13 +12556,22 @@
         <v>LF</v>
       </c>
       <c r="M217" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N217" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N217" t="str">
-        <v/>
-      </c>
-      <c r="O217">
-        <v>0</v>
+      <c r="O217" t="str">
+        <v/>
+      </c>
+      <c r="P217" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>0</v>
+      </c>
+      <c r="R217" t="str">
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -10656,13 +12612,22 @@
         <v>JC</v>
       </c>
       <c r="M218" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N218" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N218" t="str">
-        <v/>
-      </c>
-      <c r="O218">
-        <v>0</v>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+      <c r="P218" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q218">
+        <v>0</v>
+      </c>
+      <c r="R218" t="str">
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -10703,13 +12668,22 @@
         <v>JC</v>
       </c>
       <c r="M219" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N219" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N219" t="str">
-        <v/>
-      </c>
-      <c r="O219">
-        <v>0</v>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+      <c r="P219" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q219">
+        <v>0</v>
+      </c>
+      <c r="R219" t="str">
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -10750,13 +12724,22 @@
         <v>JC</v>
       </c>
       <c r="M220" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N220" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N220" t="str">
-        <v/>
-      </c>
-      <c r="O220">
-        <v>0</v>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+      <c r="P220" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>0</v>
+      </c>
+      <c r="R220" t="str">
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -10797,13 +12780,22 @@
         <v>MC</v>
       </c>
       <c r="M221" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N221" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N221" t="str">
-        <v/>
-      </c>
-      <c r="O221">
-        <v>0</v>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+      <c r="P221" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q221">
+        <v>0</v>
+      </c>
+      <c r="R221" t="str">
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -10844,13 +12836,22 @@
         <v>MC</v>
       </c>
       <c r="M222" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N222" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N222" t="str">
-        <v/>
-      </c>
-      <c r="O222">
-        <v>0</v>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+      <c r="P222" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>0</v>
+      </c>
+      <c r="R222" t="str">
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -10891,13 +12892,22 @@
         <v>MC</v>
       </c>
       <c r="M223" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N223" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N223" t="str">
-        <v/>
-      </c>
-      <c r="O223">
-        <v>0</v>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q223">
+        <v>0</v>
+      </c>
+      <c r="R223" t="str">
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -10938,13 +12948,22 @@
         <v>MC</v>
       </c>
       <c r="M224" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N224" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N224" t="str">
-        <v/>
-      </c>
-      <c r="O224">
-        <v>0</v>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q224">
+        <v>0</v>
+      </c>
+      <c r="R224" t="str">
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -10985,13 +13004,22 @@
         <v>AP</v>
       </c>
       <c r="M225" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N225" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N225" t="str">
-        <v/>
-      </c>
-      <c r="O225">
-        <v>0</v>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q225">
+        <v>0</v>
+      </c>
+      <c r="R225" t="str">
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -11032,13 +13060,22 @@
         <v>ES, MC</v>
       </c>
       <c r="M226" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N226" t="str">
         <v>Cliente C/ Pedido</v>
       </c>
-      <c r="N226" t="str">
+      <c r="O226" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="O226">
+      <c r="P226" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q226">
         <v>6</v>
+      </c>
+      <c r="R226" t="str">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -11079,13 +13116,22 @@
         <v>ES</v>
       </c>
       <c r="M227" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N227" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N227" t="str">
-        <v/>
-      </c>
-      <c r="O227">
-        <v>0</v>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+      <c r="R227" t="str">
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -11126,13 +13172,22 @@
         <v>LF</v>
       </c>
       <c r="M228" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N228" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N228" t="str">
-        <v/>
-      </c>
-      <c r="O228">
-        <v>0</v>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>0</v>
+      </c>
+      <c r="R228" t="str">
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -11173,13 +13228,22 @@
         <v>JC</v>
       </c>
       <c r="M229" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N229" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N229" t="str">
-        <v/>
-      </c>
-      <c r="O229">
-        <v>0</v>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>0</v>
+      </c>
+      <c r="R229" t="str">
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -11220,13 +13284,22 @@
         <v>JC</v>
       </c>
       <c r="M230" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N230" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N230" t="str">
-        <v/>
-      </c>
-      <c r="O230">
-        <v>0</v>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>0</v>
+      </c>
+      <c r="R230" t="str">
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -11267,13 +13340,22 @@
         <v>ES, MC</v>
       </c>
       <c r="M231" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N231" t="str">
         <v>Cliente C/ Pedido</v>
       </c>
-      <c r="N231" t="str">
+      <c r="O231" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="O231">
+      <c r="P231" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q231">
         <v>6</v>
+      </c>
+      <c r="R231" t="str">
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -11314,13 +13396,22 @@
         <v>MC</v>
       </c>
       <c r="M232" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N232" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N232" t="str">
-        <v/>
-      </c>
-      <c r="O232">
-        <v>0</v>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q232">
+        <v>0</v>
+      </c>
+      <c r="R232" t="str">
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -11361,13 +13452,22 @@
         <v>MC</v>
       </c>
       <c r="M233" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N233" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N233" t="str">
-        <v/>
-      </c>
-      <c r="O233">
-        <v>0</v>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q233">
+        <v>0</v>
+      </c>
+      <c r="R233" t="str">
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -11408,13 +13508,22 @@
         <v>AP</v>
       </c>
       <c r="M234" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N234" t="str">
         <v>Cliente Confirmado</v>
       </c>
-      <c r="N234" t="str">
-        <v/>
-      </c>
-      <c r="O234">
-        <v>0</v>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q234">
+        <v>0</v>
+      </c>
+      <c r="R234" t="str">
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -11455,13 +13564,22 @@
         <v>AP</v>
       </c>
       <c r="M235" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N235" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O235" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O235">
+      <c r="P235" t="str">
+        <v/>
+      </c>
+      <c r="Q235">
         <v>6</v>
+      </c>
+      <c r="R235" t="str">
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -11502,13 +13620,22 @@
         <v>ES</v>
       </c>
       <c r="M236" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N236" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O236" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O236">
+      <c r="P236" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q236">
         <v>6</v>
+      </c>
+      <c r="R236" t="str">
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -11549,13 +13676,22 @@
         <v>ES</v>
       </c>
       <c r="M237" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N237" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O237" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O237">
+      <c r="P237" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q237">
         <v>6</v>
+      </c>
+      <c r="R237" t="str">
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -11596,13 +13732,22 @@
         <v>ES</v>
       </c>
       <c r="M238" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N238" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O238" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O238">
+      <c r="P238" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q238">
         <v>6</v>
+      </c>
+      <c r="R238" t="str">
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -11643,13 +13788,22 @@
         <v>ES</v>
       </c>
       <c r="M239" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N239" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O239" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O239">
+      <c r="P239" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q239">
         <v>6</v>
+      </c>
+      <c r="R239" t="str">
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -11690,13 +13844,22 @@
         <v>ES</v>
       </c>
       <c r="M240" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N240" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O240" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O240">
+      <c r="P240" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q240">
         <v>6</v>
+      </c>
+      <c r="R240" t="str">
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -11737,13 +13900,22 @@
         <v>ES</v>
       </c>
       <c r="M241" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N241" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O241" t="str">
         <v>2026-07-31</v>
       </c>
-      <c r="O241">
+      <c r="P241" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q241">
         <v>6</v>
+      </c>
+      <c r="R241" t="str">
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -11784,13 +13956,22 @@
         <v>LF, JC, AP</v>
       </c>
       <c r="M242" t="str">
-        <v>Cliente Confirmado</v>
+        <v>Sim</v>
       </c>
       <c r="N242" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O242" t="str">
         <v>2026-06-12</v>
       </c>
-      <c r="O242">
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242">
         <v>6</v>
+      </c>
+      <c r="R242" t="str">
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -11831,13 +14012,22 @@
         <v>LF, JC</v>
       </c>
       <c r="M243" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N243" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O243" t="str">
         <v>2026-06-12</v>
       </c>
-      <c r="O243">
+      <c r="P243" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q243">
         <v>6</v>
+      </c>
+      <c r="R243" t="str">
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -11878,13 +14068,22 @@
         <v>AP</v>
       </c>
       <c r="M244" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N244" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O244" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O244">
+      <c r="P244" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q244">
         <v>6</v>
+      </c>
+      <c r="R244" t="str">
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -11925,13 +14124,22 @@
         <v>AP</v>
       </c>
       <c r="M245" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N245" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O245" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O245">
+      <c r="P245" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q245">
         <v>6</v>
+      </c>
+      <c r="R245" t="str">
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -11972,13 +14180,22 @@
         <v>AP</v>
       </c>
       <c r="M246" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N246" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O246" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O246">
+      <c r="P246" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q246">
         <v>6</v>
+      </c>
+      <c r="R246" t="str">
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -12019,13 +14236,22 @@
         <v>AP</v>
       </c>
       <c r="M247" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N247" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O247" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O247">
+      <c r="P247" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q247">
         <v>6</v>
+      </c>
+      <c r="R247" t="str">
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -12066,13 +14292,22 @@
         <v>AP</v>
       </c>
       <c r="M248" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N248" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O248" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O248">
+      <c r="P248" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q248">
         <v>6</v>
+      </c>
+      <c r="R248" t="str">
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -12113,18 +14348,27 @@
         <v>AP</v>
       </c>
       <c r="M249" t="str">
-        <v>Cliente Previsto</v>
+        <v>Não</v>
       </c>
       <c r="N249" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O249" t="str">
         <v>2026-12-04</v>
       </c>
-      <c r="O249">
+      <c r="P249" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q249">
         <v>6</v>
+      </c>
+      <c r="R249" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O249"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R249"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14462,280 +16706,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000B3D4C38AA931E4D9680B9EC40A2229B" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="cb5710be73f5ddbf2ffaa7a942ca047e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5099ff41-7a86-46c9-be89-1594ab5d68b8" xmlns:ns3="dc17447d-61eb-46a0-8fdb-12c42058127c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="50a6544f1ffca79c6b315887d79cb45e" ns2:_="" ns3:_="">
-    <xsd:import namespace="5099ff41-7a86-46c9-be89-1594ab5d68b8"/>
-    <xsd:import namespace="dc17447d-61eb-46a0-8fdb-12c42058127c"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:OIs" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5099ff41-7a86-46c9-be89-1594ab5d68b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="17" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="13e722c5-bebe-4801-a6ac-67aa35eba088" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OIs" ma:index="23" nillable="true" ma:displayName="OIs" ma:description="A8023641324&#10;A8023741324&#10;A8023541324" ma:format="Dropdown" ma:internalName="OIs">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dc17447d-61eb-46a0-8fdb-12c42058127c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{70266322-6b85-4550-a12c-1d5f081247e8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dc17447d-61eb-46a0-8fdb-12c42058127c">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <OIs xmlns="5099ff41-7a86-46c9-be89-1594ab5d68b8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5099ff41-7a86-46c9-be89-1594ab5d68b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="dc17447d-61eb-46a0-8fdb-12c42058127c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB6A305B-55AF-42BB-B5E3-BEDA3AB61ED0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E782410-DA6A-45B1-9DDC-37A3A0F8D75B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723C3A48-DF52-401C-B00C-A8BD1590D5DE}"/>
 </file>
--- a/Calendario_Digital_Base.xlsx
+++ b/Calendario_Digital_Base.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R249"/>
+  <dimension ref="A1:R250"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R181" t="str">
         <v/>
@@ -10655,7 +10655,7 @@
         <v>Sim</v>
       </c>
       <c r="N183" t="str">
-        <v>Cliente Previsto</v>
+        <v>Cliente Confirmado</v>
       </c>
       <c r="O183" t="str">
         <v>2026-09-18</v>
@@ -10664,7 +10664,7 @@
         <v/>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R183" t="str">
         <v/>
@@ -14366,9 +14366,65 @@
         <v/>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>svc-nextcal-1789991888343-p0574</v>
+      </c>
+      <c r="B250">
+        <v>11</v>
+      </c>
+      <c r="C250" t="str">
+        <v>CHI - Grupo CMPC - Envases</v>
+      </c>
+      <c r="D250" t="str">
+        <v/>
+      </c>
+      <c r="E250" t="str">
+        <v/>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250" t="str">
+        <v>2027-03-15</v>
+      </c>
+      <c r="K250" t="str">
+        <v>2027-03-19</v>
+      </c>
+      <c r="L250" t="str">
+        <v>LF</v>
+      </c>
+      <c r="M250" t="str">
+        <v>Não</v>
+      </c>
+      <c r="N250" t="str">
+        <v>Cliente Previsto</v>
+      </c>
+      <c r="O250" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="P250" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>6</v>
+      </c>
+      <c r="R250" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R249"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R250"/>
   </ignoredErrors>
 </worksheet>
 </file>
